--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_20_R2.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_20_R2.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.2633</v>
+        <v>6.1465</v>
       </c>
       <c r="E2" t="n">
-        <v>3.8782</v>
+        <v>4.6606</v>
       </c>
       <c r="F2" t="n">
-        <v>1.3851</v>
+        <v>1.4859</v>
       </c>
       <c r="G2" t="n">
         <v>2.3149</v>
@@ -610,13 +610,13 @@
         <v>1.6237</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.0337</v>
+        <v>-0.1505</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.9709</v>
+        <v>-0.1885</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.06279999999999999</v>
+        <v>0.038</v>
       </c>
       <c r="V2" t="n">
         <v>2.8223</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>E. ULANOVAS</t>
+          <t>L. BIRUTIS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.6204</v>
+        <v>3.4314</v>
       </c>
       <c r="E3" t="n">
-        <v>4.2598</v>
+        <v>1.9044</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.6394</v>
+        <v>1.527</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6869</v>
+        <v>2.0868</v>
       </c>
       <c r="H3" t="n">
-        <v>-2.3178</v>
+        <v>1.8726</v>
       </c>
       <c r="I3" t="n">
-        <v>3.0047</v>
+        <v>0.2142</v>
       </c>
       <c r="J3" t="n">
-        <v>2.3639</v>
+        <v>1.744</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.383</v>
+        <v>1.6336</v>
       </c>
       <c r="L3" t="n">
-        <v>2.7469</v>
+        <v>0.1104</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.677</v>
+        <v>0.3428</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.9348</v>
+        <v>0.2391</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2578</v>
+        <v>0.1038</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6959</v>
+        <v>0.9278</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.232</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>0.9278</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4876</v>
+        <v>0.6693</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3778</v>
+        <v>0.4129</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1098</v>
+        <v>0.2563</v>
       </c>
       <c r="V3" t="n">
-        <v>1.7501</v>
+        <v>-0.2525</v>
       </c>
       <c r="W3" t="n">
-        <v>1.7501</v>
+        <v>-0.2525</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>L. BIRUTIS</t>
+          <t>E. ULANOVAS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.4575</v>
+        <v>3.2666</v>
       </c>
       <c r="E4" t="n">
-        <v>1.8297</v>
+        <v>3.906</v>
       </c>
       <c r="F4" t="n">
-        <v>1.6278</v>
+        <v>-0.6394</v>
       </c>
       <c r="G4" t="n">
-        <v>2.0868</v>
+        <v>0.6869</v>
       </c>
       <c r="H4" t="n">
-        <v>1.8726</v>
+        <v>-2.3178</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2142</v>
+        <v>3.0047</v>
       </c>
       <c r="J4" t="n">
-        <v>1.744</v>
+        <v>2.3639</v>
       </c>
       <c r="K4" t="n">
-        <v>1.6336</v>
+        <v>-0.383</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1104</v>
+        <v>2.7469</v>
       </c>
       <c r="M4" t="n">
-        <v>0.3428</v>
+        <v>-1.677</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2391</v>
+        <v>-1.9348</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1038</v>
+        <v>0.2578</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9278</v>
+        <v>0.6959</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-0.232</v>
       </c>
       <c r="R4" t="n">
         <v>0.9278</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6954</v>
+        <v>0.1338</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3383</v>
+        <v>0.0239</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3572</v>
+        <v>0.1098</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.2525</v>
+        <v>1.7501</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.2525</v>
+        <v>1.7501</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9107</v>
+        <v>1.0367</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2497</v>
+        <v>0.6782</v>
       </c>
       <c r="F5" t="n">
-        <v>0.661</v>
+        <v>0.3585</v>
       </c>
       <c r="G5" t="n">
         <v>0.8452</v>
@@ -844,13 +844,13 @@
         <v>0.6959</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1665</v>
+        <v>-0.0404</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.7468</v>
+        <v>-0.3183</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5803</v>
+        <v>0.2779</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. TUBELIS</t>
+          <t>S. FRANCISCO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8722</v>
+        <v>0.9076</v>
       </c>
       <c r="E6" t="n">
-        <v>1.3812</v>
+        <v>0.7229</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.509</v>
+        <v>0.1847</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.5619</v>
+        <v>3.3603</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.7296</v>
+        <v>-1.053</v>
       </c>
       <c r="I6" t="n">
-        <v>1.1677</v>
+        <v>4.4133</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7255</v>
+        <v>3.9469</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.131</v>
+        <v>-0.4195</v>
       </c>
       <c r="L6" t="n">
-        <v>0.8564000000000001</v>
+        <v>4.3664</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.2874</v>
+        <v>-0.5865</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.5987</v>
+        <v>-0.6335</v>
       </c>
       <c r="O6" t="n">
-        <v>0.3113</v>
+        <v>0.047</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9278</v>
+        <v>-1.3917</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.232</v>
+        <v>-2.5515</v>
       </c>
       <c r="R6" t="n">
         <v>1.1598</v>
       </c>
       <c r="S6" t="n">
-        <v>0.112</v>
+        <v>-1.0921</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1845</v>
+        <v>-0.7035</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2965</v>
+        <v>-0.3886</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3943</v>
+        <v>0.031</v>
       </c>
       <c r="W6" t="n">
-        <v>1.0722</v>
+        <v>0.031</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.6778999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S. FRANCISCO</t>
+          <t>A. TUBELIS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3378</v>
+        <v>0.6609</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4556</v>
+        <v>1.338</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1178</v>
+        <v>-0.677</v>
       </c>
       <c r="G7" t="n">
-        <v>3.3603</v>
+        <v>-0.5619</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.053</v>
+        <v>-1.7296</v>
       </c>
       <c r="I7" t="n">
-        <v>4.4133</v>
+        <v>1.1677</v>
       </c>
       <c r="J7" t="n">
-        <v>3.9469</v>
+        <v>0.7255</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.4195</v>
+        <v>-0.131</v>
       </c>
       <c r="L7" t="n">
-        <v>4.3664</v>
+        <v>0.8564000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.5865</v>
+        <v>-1.2874</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.6335</v>
+        <v>-1.5987</v>
       </c>
       <c r="O7" t="n">
-        <v>0.047</v>
+        <v>0.3113</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.3917</v>
+        <v>0.9278</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.5515</v>
+        <v>-0.232</v>
       </c>
       <c r="R7" t="n">
         <v>1.1598</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.6619</v>
+        <v>-0.0993</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.9709</v>
+        <v>-0.2278</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.6909999999999999</v>
+        <v>0.1285</v>
       </c>
       <c r="V7" t="n">
-        <v>0.031</v>
+        <v>0.3943</v>
       </c>
       <c r="W7" t="n">
-        <v>0.031</v>
+        <v>1.0722</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.6778999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3051</v>
+        <v>-0.2607</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.2556</v>
+        <v>-1.8886</v>
       </c>
       <c r="F8" t="n">
-        <v>1.5607</v>
+        <v>1.6279</v>
       </c>
       <c r="G8" t="n">
         <v>-0.9282</v>
@@ -1078,13 +1078,13 @@
         <v>0.9278</v>
       </c>
       <c r="S8" t="n">
-        <v>1.303</v>
+        <v>0.7371</v>
       </c>
       <c r="T8" t="n">
-        <v>1.0499</v>
+        <v>0.4169</v>
       </c>
       <c r="U8" t="n">
-        <v>0.253</v>
+        <v>0.3203</v>
       </c>
       <c r="V8" t="n">
         <v>0.3943</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.7747000000000001</v>
+        <v>-0.7411</v>
       </c>
       <c r="E9" t="n">
         <v>-0.0043</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.7704</v>
+        <v>-0.7368</v>
       </c>
       <c r="G9" t="n">
         <v>-0.498</v>
@@ -1156,13 +1156,13 @@
         <v>0.232</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3668</v>
+        <v>-0.3332</v>
       </c>
       <c r="T9" t="n">
         <v>-0.0747</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2921</v>
+        <v>-0.2585</v>
       </c>
       <c r="V9" t="n">
         <v>-0.1418</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.761</v>
+        <v>-1.3736</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.9536</v>
+        <v>-1.5997</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1925</v>
+        <v>0.2262</v>
       </c>
       <c r="G10" t="n">
         <v>-1.7166</v>
@@ -1234,13 +1234,13 @@
         <v>0.4639</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5083</v>
+        <v>-0.1208</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4481</v>
+        <v>-0.09420000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0602</v>
+        <v>-0.0266</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.2089</v>
+        <v>-2.2521</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.1566</v>
+        <v>-2.1999</v>
       </c>
       <c r="F11" t="n">
         <v>-0.0523</v>
@@ -1312,10 +1312,10 @@
         <v>0.9278</v>
       </c>
       <c r="S11" t="n">
-        <v>0.08260000000000001</v>
+        <v>0.0393</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0351</v>
+        <v>-0.0784</v>
       </c>
       <c r="U11" t="n">
         <v>0.1177</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.0984</v>
+        <v>-3.4784</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.7544</v>
+        <v>-3.0336</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.344</v>
+        <v>-0.4448</v>
       </c>
       <c r="G12" t="n">
         <v>0.3864</v>
@@ -1390,13 +1390,13 @@
         <v>1.3917</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.539</v>
+        <v>-0.919</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3339</v>
+        <v>-0.613</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2051</v>
+        <v>-0.306</v>
       </c>
       <c r="V12" t="n">
         <v>-0.3943</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.088</v>
+        <v>-3.761</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.4803</v>
+        <v>-4.2877</v>
       </c>
       <c r="F13" t="n">
-        <v>0.3923</v>
+        <v>0.5266999999999999</v>
       </c>
       <c r="G13" t="n">
         <v>-0.3271</v>
@@ -1468,13 +1468,13 @@
         <v>1.1598</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.7635</v>
+        <v>-0.4364</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.2987</v>
+        <v>-0.1061</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.4648</v>
+        <v>-0.3304</v>
       </c>
       <c r="V13" t="n">
         <v>-0.6778999999999999</v>
@@ -1501,16 +1501,16 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.836000000000001</v>
+        <v>3.5828</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.5505999999999998</v>
+        <v>0.1962999999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>3.386500000000001</v>
+        <v>3.3866</v>
       </c>
       <c r="G14" t="n">
-        <v>2.517000000000001</v>
+        <v>2.516999999999999</v>
       </c>
       <c r="H14" t="n">
         <v>-4.3091</v>
@@ -1519,13 +1519,13 @@
         <v>6.826</v>
       </c>
       <c r="J14" t="n">
-        <v>9.563199999999998</v>
+        <v>9.563200000000002</v>
       </c>
       <c r="K14" t="n">
         <v>5.063699999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>4.499599999999999</v>
+        <v>4.4996</v>
       </c>
       <c r="M14" t="n">
         <v>-7.046200000000001</v>
@@ -1546,13 +1546,13 @@
         <v>11.5978</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.3591</v>
+        <v>-1.6122</v>
       </c>
       <c r="T14" t="n">
-        <v>-2.2976</v>
+        <v>-1.5508</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.06149999999999994</v>
+        <v>-0.06160000000000015</v>
       </c>
       <c r="V14" t="n">
         <v>4.9977</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>8.389699999999999</v>
+        <v>9.3498</v>
       </c>
       <c r="E15" t="n">
-        <v>7.9075</v>
+        <v>8.7332</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4822</v>
+        <v>0.6166</v>
       </c>
       <c r="G15" t="n">
         <v>6.8513</v>
@@ -1624,13 +1624,13 @@
         <v>2.0876</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2091</v>
+        <v>0.751</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.8057</v>
+        <v>0.02</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5966</v>
+        <v>0.731</v>
       </c>
       <c r="V15" t="n">
         <v>0.8197</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.1268</v>
+        <v>3.5643</v>
       </c>
       <c r="E16" t="n">
-        <v>0.3783</v>
+        <v>0.6142</v>
       </c>
       <c r="F16" t="n">
-        <v>2.7484</v>
+        <v>2.95</v>
       </c>
       <c r="G16" t="n">
         <v>2.7581</v>
@@ -1702,13 +1702,13 @@
         <v>1.6237</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.8839</v>
+        <v>-0.4463</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4481</v>
+        <v>-0.2122</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4358</v>
+        <v>-0.2341</v>
       </c>
       <c r="V16" t="n">
         <v>0.7886</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.5615</v>
+        <v>2.8482</v>
       </c>
       <c r="E17" t="n">
-        <v>1.4782</v>
+        <v>1.832</v>
       </c>
       <c r="F17" t="n">
-        <v>1.0834</v>
+        <v>1.0162</v>
       </c>
       <c r="G17" t="n">
         <v>3.4545</v>
@@ -1780,13 +1780,13 @@
         <v>2.3195</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1792</v>
+        <v>0.4659</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2434</v>
+        <v>0.1105</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4226</v>
+        <v>0.3554</v>
       </c>
       <c r="V17" t="n">
         <v>-1.0722</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5658</v>
+        <v>0.177</v>
       </c>
       <c r="E18" t="n">
-        <v>2.1125</v>
+        <v>1.2868</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.5467</v>
+        <v>-1.1098</v>
       </c>
       <c r="G18" t="n">
         <v>0.49</v>
@@ -1858,13 +1858,13 @@
         <v>1.6237</v>
       </c>
       <c r="S18" t="n">
-        <v>1.2744</v>
+        <v>0.8856000000000001</v>
       </c>
       <c r="T18" t="n">
-        <v>1.404</v>
+        <v>0.5783</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1296</v>
+        <v>0.3073</v>
       </c>
       <c r="V18" t="n">
         <v>-2.8223</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.5026</v>
+        <v>-1.1253</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.0984</v>
+        <v>-1.4523</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5958</v>
+        <v>0.327</v>
       </c>
       <c r="G20" t="n">
         <v>-1.1503</v>
@@ -2014,13 +2014,13 @@
         <v>0.6959</v>
       </c>
       <c r="S20" t="n">
-        <v>0.5755</v>
+        <v>-0.0472</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1889</v>
+        <v>-0.165</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3866</v>
+        <v>0.1177</v>
       </c>
       <c r="V20" t="n">
         <v>0.5361</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. BACOT JR.</t>
+          <t>N. MELLI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.0849</v>
+        <v>-1.4632</v>
       </c>
       <c r="E21" t="n">
-        <v>1.4018</v>
+        <v>-2.3114</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.4867</v>
+        <v>0.8483000000000001</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.9265</v>
+        <v>-3.3835</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3516</v>
+        <v>0.5248</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.2781</v>
+        <v>-3.9082</v>
       </c>
       <c r="J21" t="n">
-        <v>0.9142</v>
+        <v>-1.5176</v>
       </c>
       <c r="K21" t="n">
-        <v>0.8773</v>
+        <v>1.1259</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0368</v>
+        <v>-2.6436</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.8406</v>
+        <v>-1.8659</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.5256999999999999</v>
+        <v>-0.6012</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.3149</v>
+        <v>-1.2647</v>
       </c>
       <c r="P21" t="n">
-        <v>0.6959</v>
+        <v>0.9278</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R21" t="n">
-        <v>0.6959</v>
+        <v>2.0876</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2179</v>
+        <v>1.1343</v>
       </c>
       <c r="T21" t="n">
-        <v>0.4876</v>
+        <v>0.3659</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2697</v>
+        <v>0.7683</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.0722</v>
+        <v>-0.1418</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.0722</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>N. MELLI</t>
+          <t>A. BACOT JR.</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.6319</v>
+        <v>-1.4895</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.5473</v>
+        <v>0.93</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9155</v>
+        <v>-2.4195</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.3835</v>
+        <v>-0.9265</v>
       </c>
       <c r="H22" t="n">
-        <v>0.5248</v>
+        <v>0.3516</v>
       </c>
       <c r="I22" t="n">
-        <v>-3.9082</v>
+        <v>-1.2781</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.5176</v>
+        <v>0.9142</v>
       </c>
       <c r="K22" t="n">
-        <v>1.1259</v>
+        <v>0.8773</v>
       </c>
       <c r="L22" t="n">
-        <v>-2.6436</v>
+        <v>0.0368</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.8659</v>
+        <v>-1.8406</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.6012</v>
+        <v>-0.5256999999999999</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.2647</v>
+        <v>-1.3149</v>
       </c>
       <c r="P22" t="n">
-        <v>0.9278</v>
+        <v>0.6959</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.0876</v>
+        <v>0.6959</v>
       </c>
       <c r="S22" t="n">
-        <v>0.9656</v>
+        <v>-0.1867</v>
       </c>
       <c r="T22" t="n">
-        <v>0.13</v>
+        <v>0.0158</v>
       </c>
       <c r="U22" t="n">
-        <v>0.8356</v>
+        <v>-0.2025</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.1418</v>
+        <v>-1.0722</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.1418</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.2876</v>
+        <v>-3.051</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.3755</v>
+        <v>-2.9037</v>
       </c>
       <c r="F23" t="n">
-        <v>0.08790000000000001</v>
+        <v>-0.1473</v>
       </c>
       <c r="G23" t="n">
         <v>-2.651</v>
@@ -2248,13 +2248,13 @@
         <v>0.4639</v>
       </c>
       <c r="S23" t="n">
-        <v>0.0593</v>
+        <v>0.2959</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4481</v>
+        <v>0.0237</v>
       </c>
       <c r="U23" t="n">
-        <v>0.5074</v>
+        <v>0.2721</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.5914</v>
+        <v>-4.3828</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.798</v>
+        <v>-4.3877</v>
       </c>
       <c r="F24" t="n">
-        <v>0.2066</v>
+        <v>0.0049</v>
       </c>
       <c r="G24" t="n">
         <v>-3.0162</v>
@@ -2326,13 +2326,13 @@
         <v>0.6959</v>
       </c>
       <c r="S24" t="n">
-        <v>1.332</v>
+        <v>0.5406</v>
       </c>
       <c r="T24" t="n">
-        <v>0.767</v>
+        <v>0.1772</v>
       </c>
       <c r="U24" t="n">
-        <v>0.5649</v>
+        <v>0.3633</v>
       </c>
       <c r="V24" t="n">
         <v>-0.2836</v>
@@ -2359,10 +2359,10 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.9077</v>
+        <v>-6.7897</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.3136</v>
+        <v>-4.1956</v>
       </c>
       <c r="F25" t="n">
         <v>-2.5941</v>
@@ -2404,10 +2404,10 @@
         <v>1.1598</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.8452</v>
+        <v>-0.7272999999999999</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.8215</v>
+        <v>-0.7035</v>
       </c>
       <c r="U25" t="n">
         <v>-0.0237</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-2.835900000000001</v>
+        <v>-2.835800000000001</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.919800000000001</v>
+        <v>-1.919799999999999</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.9159999999999995</v>
+        <v>-0.9159999999999999</v>
       </c>
       <c r="G26" t="n">
         <v>-2.5169</v>
@@ -2482,13 +2482,13 @@
         <v>13.9174</v>
       </c>
       <c r="S26" t="n">
-        <v>2.3591</v>
+        <v>2.3592</v>
       </c>
       <c r="T26" t="n">
-        <v>0.0612999999999998</v>
+        <v>0.06130000000000013</v>
       </c>
       <c r="U26" t="n">
-        <v>2.2976</v>
+        <v>2.2975</v>
       </c>
       <c r="V26" t="n">
         <v>-4.9978</v>
